--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N76_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N76_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.826500649022971</v>
+        <v>1.109306355466233</v>
       </c>
       <c r="D2" t="n">
-        <v>69.6262671956206</v>
+        <v>11.31426841928835</v>
       </c>
       <c r="E2" t="n">
-        <v>12.46817552689864</v>
+        <v>2.02607852312103</v>
       </c>
       <c r="F2" t="n">
-        <v>17.78909547780509</v>
+        <v>2.890728015143328</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.93411274517317</v>
+        <v>6.16429332109064</v>
       </c>
       <c r="D3" t="n">
-        <v>44.05850958040342</v>
+        <v>7.159507806815555</v>
       </c>
       <c r="E3" t="n">
-        <v>12.46817552689864</v>
+        <v>2.02607852312103</v>
       </c>
       <c r="F3" t="n">
-        <v>17.78909547780509</v>
+        <v>2.890728015143328</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.80423141657769</v>
+        <v>3.218187605193874</v>
       </c>
       <c r="D4" t="n">
-        <v>20.10620014497037</v>
+        <v>3.267257523557685</v>
       </c>
       <c r="E4" t="n">
-        <v>12.46817552689864</v>
+        <v>2.02607852312103</v>
       </c>
       <c r="F4" t="n">
-        <v>17.78909547780509</v>
+        <v>2.890728015143328</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.86606344467511</v>
+        <v>5.665735309759705</v>
       </c>
       <c r="D5" t="n">
-        <v>37.36242658834313</v>
+        <v>6.071394320605759</v>
       </c>
       <c r="E5" t="n">
-        <v>12.46817552689864</v>
+        <v>2.02607852312103</v>
       </c>
       <c r="F5" t="n">
-        <v>17.78909547780509</v>
+        <v>2.890728015143328</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
